--- a/mallar/Protokoll/Protokoll 2019 individuell klass_(mall).xlsx
+++ b/mallar/Protokoll/Protokoll 2019 individuell klass_(mall).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\episerver\voltige\VoltigeClosedXML\mallar\Protokoll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1855BF32-935B-4751-80F7-AB3C821FFB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B26499-7AEB-4042-9AFD-3ABBC928D337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="966" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13096" tabRatio="966" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="37" r:id="rId1"/>
@@ -3199,6 +3199,227 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3231,223 +3452,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="56" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3491,9 +3497,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3683,6 +3686,45 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
     </xf>
@@ -3695,45 +3737,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
     </xf>
@@ -3742,9 +3745,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -6376,10 +6376,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -6393,10 +6393,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -6425,30 +6425,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" ht="8.65" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6462,16 +6462,16 @@
       <c r="A13" s="279" t="s">
         <v>168</v>
       </c>
-      <c r="B13" s="429" t="s">
+      <c r="B13" s="430" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="430"/>
-      <c r="D13" s="430"/>
-      <c r="E13" s="430"/>
-      <c r="F13" s="430"/>
-      <c r="G13" s="430"/>
-      <c r="H13" s="430"/>
-      <c r="I13" s="431"/>
+      <c r="C13" s="431"/>
+      <c r="D13" s="431"/>
+      <c r="E13" s="431"/>
+      <c r="F13" s="431"/>
+      <c r="G13" s="431"/>
+      <c r="H13" s="431"/>
+      <c r="I13" s="432"/>
       <c r="J13" s="18" t="s">
         <v>170</v>
       </c>
@@ -6482,19 +6482,19 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="413" t="s">
+      <c r="A14" s="414" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="415" t="s">
+      <c r="B14" s="416" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="416"/>
-      <c r="D14" s="416"/>
-      <c r="E14" s="416"/>
-      <c r="F14" s="416"/>
-      <c r="G14" s="416"/>
-      <c r="H14" s="416"/>
-      <c r="I14" s="417"/>
+      <c r="C14" s="417"/>
+      <c r="D14" s="417"/>
+      <c r="E14" s="417"/>
+      <c r="F14" s="417"/>
+      <c r="G14" s="417"/>
+      <c r="H14" s="417"/>
+      <c r="I14" s="418"/>
       <c r="J14" s="18" t="s">
         <v>112</v>
       </c>
@@ -6505,17 +6505,17 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="123" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="435"/>
-      <c r="B15" s="436" t="s">
+      <c r="A15" s="436"/>
+      <c r="B15" s="437" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="419"/>
-      <c r="D15" s="419"/>
-      <c r="E15" s="419"/>
-      <c r="F15" s="419"/>
-      <c r="G15" s="419"/>
-      <c r="H15" s="419"/>
-      <c r="I15" s="420"/>
+      <c r="C15" s="420"/>
+      <c r="D15" s="420"/>
+      <c r="E15" s="420"/>
+      <c r="F15" s="420"/>
+      <c r="G15" s="420"/>
+      <c r="H15" s="420"/>
+      <c r="I15" s="421"/>
       <c r="J15" s="20" t="s">
         <v>175</v>
       </c>
@@ -6526,19 +6526,19 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="413" t="s">
+      <c r="A16" s="414" t="s">
         <v>201</v>
       </c>
-      <c r="B16" s="432" t="s">
+      <c r="B16" s="433" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="433"/>
-      <c r="D16" s="433"/>
-      <c r="E16" s="433"/>
-      <c r="F16" s="433"/>
-      <c r="G16" s="433"/>
-      <c r="H16" s="433"/>
-      <c r="I16" s="434"/>
+      <c r="C16" s="434"/>
+      <c r="D16" s="434"/>
+      <c r="E16" s="434"/>
+      <c r="F16" s="434"/>
+      <c r="G16" s="434"/>
+      <c r="H16" s="434"/>
+      <c r="I16" s="435"/>
       <c r="J16" s="18" t="s">
         <v>176</v>
       </c>
@@ -6549,17 +6549,17 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="414"/>
-      <c r="B17" s="426" t="s">
+      <c r="A17" s="415"/>
+      <c r="B17" s="427" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="427"/>
-      <c r="D17" s="427"/>
-      <c r="E17" s="427"/>
-      <c r="F17" s="427"/>
-      <c r="G17" s="427"/>
-      <c r="H17" s="427"/>
-      <c r="I17" s="428"/>
+      <c r="C17" s="428"/>
+      <c r="D17" s="428"/>
+      <c r="E17" s="428"/>
+      <c r="F17" s="428"/>
+      <c r="G17" s="428"/>
+      <c r="H17" s="428"/>
+      <c r="I17" s="429"/>
       <c r="J17" s="19" t="s">
         <v>177</v>
       </c>
@@ -7337,10 +7337,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -7354,10 +7354,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -7386,30 +7386,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" ht="10.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="22.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7423,16 +7423,16 @@
       <c r="A13" s="279" t="s">
         <v>168</v>
       </c>
-      <c r="B13" s="429" t="s">
+      <c r="B13" s="430" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="430"/>
-      <c r="D13" s="430"/>
-      <c r="E13" s="430"/>
-      <c r="F13" s="430"/>
-      <c r="G13" s="430"/>
-      <c r="H13" s="430"/>
-      <c r="I13" s="431"/>
+      <c r="C13" s="431"/>
+      <c r="D13" s="431"/>
+      <c r="E13" s="431"/>
+      <c r="F13" s="431"/>
+      <c r="G13" s="431"/>
+      <c r="H13" s="431"/>
+      <c r="I13" s="432"/>
       <c r="J13" s="18" t="s">
         <v>170</v>
       </c>
@@ -7443,19 +7443,19 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="85.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="413" t="s">
+      <c r="A14" s="414" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="415" t="s">
+      <c r="B14" s="416" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="416"/>
-      <c r="D14" s="416"/>
-      <c r="E14" s="416"/>
-      <c r="F14" s="416"/>
-      <c r="G14" s="416"/>
-      <c r="H14" s="416"/>
-      <c r="I14" s="417"/>
+      <c r="C14" s="417"/>
+      <c r="D14" s="417"/>
+      <c r="E14" s="417"/>
+      <c r="F14" s="417"/>
+      <c r="G14" s="417"/>
+      <c r="H14" s="417"/>
+      <c r="I14" s="418"/>
       <c r="J14" s="18" t="s">
         <v>188</v>
       </c>
@@ -7466,17 +7466,17 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="435"/>
-      <c r="B15" s="415" t="s">
+      <c r="A15" s="436"/>
+      <c r="B15" s="416" t="s">
         <v>186</v>
       </c>
-      <c r="C15" s="416"/>
-      <c r="D15" s="416"/>
-      <c r="E15" s="416"/>
-      <c r="F15" s="416"/>
-      <c r="G15" s="416"/>
-      <c r="H15" s="416"/>
-      <c r="I15" s="417"/>
+      <c r="C15" s="417"/>
+      <c r="D15" s="417"/>
+      <c r="E15" s="417"/>
+      <c r="F15" s="417"/>
+      <c r="G15" s="417"/>
+      <c r="H15" s="417"/>
+      <c r="I15" s="418"/>
       <c r="J15" s="20" t="s">
         <v>175</v>
       </c>
@@ -7487,19 +7487,19 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="413" t="s">
+      <c r="A16" s="414" t="s">
         <v>201</v>
       </c>
-      <c r="B16" s="432" t="s">
+      <c r="B16" s="433" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="433"/>
-      <c r="D16" s="433"/>
-      <c r="E16" s="433"/>
-      <c r="F16" s="433"/>
-      <c r="G16" s="433"/>
-      <c r="H16" s="433"/>
-      <c r="I16" s="434"/>
+      <c r="C16" s="434"/>
+      <c r="D16" s="434"/>
+      <c r="E16" s="434"/>
+      <c r="F16" s="434"/>
+      <c r="G16" s="434"/>
+      <c r="H16" s="434"/>
+      <c r="I16" s="435"/>
       <c r="J16" s="18" t="s">
         <v>189</v>
       </c>
@@ -7510,17 +7510,17 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="414"/>
-      <c r="B17" s="426" t="s">
+      <c r="A17" s="415"/>
+      <c r="B17" s="427" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="427"/>
-      <c r="D17" s="427"/>
-      <c r="E17" s="427"/>
-      <c r="F17" s="427"/>
-      <c r="G17" s="427"/>
-      <c r="H17" s="427"/>
-      <c r="I17" s="428"/>
+      <c r="C17" s="428"/>
+      <c r="D17" s="428"/>
+      <c r="E17" s="428"/>
+      <c r="F17" s="428"/>
+      <c r="G17" s="428"/>
+      <c r="H17" s="428"/>
+      <c r="I17" s="429"/>
       <c r="J17" s="19" t="s">
         <v>136</v>
       </c>
@@ -7629,11 +7629,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C10:F10"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:I14"/>
@@ -7641,6 +7636,11 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B17:I17"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C10:F10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="K13 K14 K15 K16 K17 L20" xr:uid="{D6E2C8F8-7AAD-4E82-B818-AA02695B4DF9}">
@@ -7726,10 +7726,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -7743,10 +7743,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7769,30 +7769,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -7818,30 +7818,32 @@
       </c>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="437" t="s">
+      <c r="A15" s="438" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="438"/>
-      <c r="C15" s="438"/>
-      <c r="D15" s="438"/>
-      <c r="E15" s="438"/>
-      <c r="F15" s="439"/>
+      <c r="B15" s="439"/>
+      <c r="C15" s="439"/>
+      <c r="D15" s="439"/>
+      <c r="E15" s="439"/>
+      <c r="F15" s="440"/>
       <c r="G15" s="33"/>
       <c r="H15" s="33"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="36"/>
-      <c r="L15" s="245"/>
+      <c r="L15" s="245">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="440" t="s">
+      <c r="A16" s="441" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="441"/>
-      <c r="C16" s="441"/>
-      <c r="D16" s="441"/>
-      <c r="E16" s="441"/>
-      <c r="F16" s="442"/>
+      <c r="B16" s="442"/>
+      <c r="C16" s="442"/>
+      <c r="D16" s="442"/>
+      <c r="E16" s="442"/>
+      <c r="F16" s="443"/>
       <c r="G16" s="33"/>
       <c r="H16" s="33"/>
       <c r="I16" s="11"/>
@@ -7902,27 +7904,27 @@
       <c r="L20" s="138"/>
     </row>
     <row r="21" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="446" t="s">
+      <c r="A21" s="447" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="447"/>
-      <c r="C21" s="447"/>
-      <c r="D21" s="447"/>
-      <c r="E21" s="447"/>
-      <c r="F21" s="447"/>
-      <c r="G21" s="447"/>
-      <c r="H21" s="447"/>
-      <c r="I21" s="447"/>
+      <c r="B21" s="448"/>
+      <c r="C21" s="448"/>
+      <c r="D21" s="448"/>
+      <c r="E21" s="448"/>
+      <c r="F21" s="448"/>
+      <c r="G21" s="448"/>
+      <c r="H21" s="448"/>
+      <c r="I21" s="448"/>
       <c r="J21" s="137"/>
       <c r="K21" s="136"/>
       <c r="L21" s="8"/>
       <c r="R21" s="131"/>
     </row>
     <row r="22" spans="1:18" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="454" t="s">
+      <c r="A22" s="455" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="455"/>
+      <c r="B22" s="456"/>
       <c r="C22" s="135"/>
       <c r="D22" s="135"/>
       <c r="E22" s="135"/>
@@ -7936,15 +7938,15 @@
       <c r="R22" s="131"/>
     </row>
     <row r="23" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="450" t="s">
+      <c r="A23" s="451" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="451"/>
+      <c r="B23" s="452"/>
       <c r="C23" s="254"/>
-      <c r="D23" s="448" t="s">
+      <c r="D23" s="449" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="449"/>
+      <c r="E23" s="450"/>
       <c r="F23" s="255"/>
       <c r="G23" s="214" t="s">
         <v>63</v>
@@ -7967,11 +7969,11 @@
       <c r="R23" s="131"/>
     </row>
     <row r="24" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="452" t="s">
+      <c r="A24" s="453" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="453"/>
-      <c r="C24" s="453"/>
+      <c r="B24" s="454"/>
+      <c r="C24" s="454"/>
       <c r="D24" s="218"/>
       <c r="E24" s="218"/>
       <c r="F24" s="218"/>
@@ -7983,19 +7985,19 @@
       <c r="R24" s="131"/>
     </row>
     <row r="25" spans="1:18" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="443" t="s">
+      <c r="A25" s="444" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="444"/>
-      <c r="C25" s="444"/>
-      <c r="D25" s="444"/>
-      <c r="E25" s="444"/>
-      <c r="F25" s="444"/>
-      <c r="G25" s="444"/>
-      <c r="H25" s="444"/>
-      <c r="I25" s="444"/>
-      <c r="J25" s="444"/>
-      <c r="K25" s="445"/>
+      <c r="B25" s="445"/>
+      <c r="C25" s="445"/>
+      <c r="D25" s="445"/>
+      <c r="E25" s="445"/>
+      <c r="F25" s="445"/>
+      <c r="G25" s="445"/>
+      <c r="H25" s="445"/>
+      <c r="I25" s="445"/>
+      <c r="J25" s="445"/>
+      <c r="K25" s="446"/>
       <c r="L25" s="9">
         <f>IFERROR(K23-K24,0)</f>
         <v>0</v>
@@ -8127,18 +8129,22 @@
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C10:F10"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="L15:L19" xr:uid="{924DC316-F573-4895-AFCD-D14BE73F69A0}">
-      <formula1>1</formula1>
+  <dataValidations count="3">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="L19" xr:uid="{924DC316-F573-4895-AFCD-D14BE73F69A0}">
+      <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror. Var noga med punkt eller komma beroende på språk" sqref="C23 F23 K24" xr:uid="{AC54A561-64AF-48D6-AEDB-6E880CE3EDA4}">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="L15 L16 L17 L18" xr:uid="{2769405F-640D-4C69-80AB-20B3D67BE737}">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;L&amp;G&amp;C&amp;"Verdana,Normal"&amp;12PROTOKOLL FÖR INDIVIDUELL TÄVLAN</oddHeader>
     <oddFooter>&amp;R2022-01-01</oddFooter>
@@ -8214,10 +8220,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -8231,10 +8237,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8257,30 +8263,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8306,14 +8312,14 @@
       </c>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="437" t="s">
+      <c r="A15" s="438" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="438"/>
-      <c r="C15" s="438"/>
-      <c r="D15" s="438"/>
-      <c r="E15" s="438"/>
-      <c r="F15" s="439"/>
+      <c r="B15" s="439"/>
+      <c r="C15" s="439"/>
+      <c r="D15" s="439"/>
+      <c r="E15" s="439"/>
+      <c r="F15" s="440"/>
       <c r="G15" s="33"/>
       <c r="H15" s="33"/>
       <c r="I15" s="11"/>
@@ -8322,14 +8328,14 @@
       <c r="L15" s="245"/>
     </row>
     <row r="16" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="440" t="s">
+      <c r="A16" s="441" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="441"/>
-      <c r="C16" s="441"/>
-      <c r="D16" s="441"/>
-      <c r="E16" s="441"/>
-      <c r="F16" s="442"/>
+      <c r="B16" s="442"/>
+      <c r="C16" s="442"/>
+      <c r="D16" s="442"/>
+      <c r="E16" s="442"/>
+      <c r="F16" s="443"/>
       <c r="G16" s="33"/>
       <c r="H16" s="33"/>
       <c r="I16" s="11"/>
@@ -8390,27 +8396,27 @@
       <c r="L20" s="138"/>
     </row>
     <row r="21" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="446" t="s">
+      <c r="A21" s="447" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="447"/>
-      <c r="C21" s="447"/>
-      <c r="D21" s="447"/>
-      <c r="E21" s="447"/>
-      <c r="F21" s="447"/>
-      <c r="G21" s="447"/>
-      <c r="H21" s="447"/>
-      <c r="I21" s="447"/>
+      <c r="B21" s="448"/>
+      <c r="C21" s="448"/>
+      <c r="D21" s="448"/>
+      <c r="E21" s="448"/>
+      <c r="F21" s="448"/>
+      <c r="G21" s="448"/>
+      <c r="H21" s="448"/>
+      <c r="I21" s="448"/>
       <c r="J21" s="137"/>
       <c r="K21" s="136"/>
       <c r="L21" s="8"/>
       <c r="R21" s="131"/>
     </row>
     <row r="22" spans="1:18" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="454" t="s">
+      <c r="A22" s="455" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="455"/>
+      <c r="B22" s="456"/>
       <c r="C22" s="135"/>
       <c r="D22" s="135"/>
       <c r="E22" s="135"/>
@@ -8424,15 +8430,15 @@
       <c r="R22" s="131"/>
     </row>
     <row r="23" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="450" t="s">
+      <c r="A23" s="451" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="451"/>
+      <c r="B23" s="452"/>
       <c r="C23" s="254"/>
-      <c r="D23" s="448" t="s">
+      <c r="D23" s="449" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="449"/>
+      <c r="E23" s="450"/>
       <c r="F23" s="255"/>
       <c r="G23" s="214" t="s">
         <v>63</v>
@@ -8455,11 +8461,11 @@
       <c r="R23" s="131"/>
     </row>
     <row r="24" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="452" t="s">
+      <c r="A24" s="453" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="453"/>
-      <c r="C24" s="453"/>
+      <c r="B24" s="454"/>
+      <c r="C24" s="454"/>
       <c r="D24" s="218"/>
       <c r="E24" s="218"/>
       <c r="F24" s="218"/>
@@ -8471,19 +8477,19 @@
       <c r="R24" s="131"/>
     </row>
     <row r="25" spans="1:18" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="443" t="s">
+      <c r="A25" s="444" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="444"/>
-      <c r="C25" s="444"/>
-      <c r="D25" s="444"/>
-      <c r="E25" s="444"/>
-      <c r="F25" s="444"/>
-      <c r="G25" s="444"/>
-      <c r="H25" s="444"/>
-      <c r="I25" s="444"/>
-      <c r="J25" s="444"/>
-      <c r="K25" s="445"/>
+      <c r="B25" s="445"/>
+      <c r="C25" s="445"/>
+      <c r="D25" s="445"/>
+      <c r="E25" s="445"/>
+      <c r="F25" s="445"/>
+      <c r="G25" s="445"/>
+      <c r="H25" s="445"/>
+      <c r="I25" s="445"/>
+      <c r="J25" s="445"/>
+      <c r="K25" s="446"/>
       <c r="L25" s="9">
         <f>IFERROR(K23-K24,0)</f>
         <v>0</v>
@@ -8601,6 +8607,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A21:I21"/>
@@ -8608,25 +8620,23 @@
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="L15:L19" xr:uid="{A69A740B-83B6-42AF-8E6A-DFC2DE5E21F4}">
-      <formula1>1</formula1>
+  <dataValidations count="3">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="L19" xr:uid="{A69A740B-83B6-42AF-8E6A-DFC2DE5E21F4}">
+      <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror. Var noga med punkt eller komma beroende på språk" sqref="C23 F23 K24" xr:uid="{FFAA6551-97BA-4962-93F4-8BCF71A28866}">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="L15 L16 L17 L18" xr:uid="{E120D96D-9E66-412F-819C-0BAAF53F0A22}">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;L&amp;G&amp;C&amp;"Verdana,Normal"&amp;12PROTOKOLL FÖR INDIVIDUELL TÄVLAN</oddHeader>
     <oddFooter>&amp;R2022-01-01</oddFooter>
@@ -9228,17 +9238,17 @@
   <sheetData>
     <row r="1" spans="1:12" s="111" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="464" t="s">
+      <c r="A2" s="461" t="s">
         <v>155</v>
       </c>
-      <c r="B2" s="464"/>
-      <c r="C2" s="464"/>
-      <c r="D2" s="464"/>
-      <c r="E2" s="464"/>
-      <c r="F2" s="464"/>
-      <c r="G2" s="464"/>
-      <c r="H2" s="464"/>
-      <c r="I2" s="464"/>
+      <c r="B2" s="461"/>
+      <c r="C2" s="461"/>
+      <c r="D2" s="461"/>
+      <c r="E2" s="461"/>
+      <c r="F2" s="461"/>
+      <c r="G2" s="461"/>
+      <c r="H2" s="461"/>
+      <c r="I2" s="461"/>
       <c r="J2" s="141"/>
       <c r="K2" s="141"/>
       <c r="L2" s="141"/>
@@ -9283,10 +9293,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="G5" s="140"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
@@ -9301,10 +9311,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="G6" s="139"/>
       <c r="H6" s="13"/>
       <c r="I6" s="14" t="s">
@@ -9335,10 +9345,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
       <c r="G8" s="149"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -9353,10 +9363,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
       <c r="G9" s="149"/>
       <c r="H9" s="139"/>
       <c r="I9" s="139"/>
@@ -9369,15 +9379,15 @@
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
       <c r="G10" s="149"/>
       <c r="H10" s="139"/>
       <c r="I10" s="139"/>
-      <c r="J10" s="460"/>
-      <c r="K10" s="460"/>
+      <c r="J10" s="457"/>
+      <c r="K10" s="457"/>
       <c r="L10" s="150"/>
     </row>
     <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -9404,10 +9414,10 @@
       <c r="C13" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="465" t="s">
+      <c r="D13" s="462" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="466"/>
+      <c r="E13" s="463"/>
       <c r="F13" s="237" t="s">
         <v>116</v>
       </c>
@@ -9420,10 +9430,10 @@
       <c r="I13" s="239" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="469" t="s">
+      <c r="J13" s="466" t="s">
         <v>121</v>
       </c>
-      <c r="K13" s="470"/>
+      <c r="K13" s="467"/>
       <c r="L13" s="148"/>
     </row>
     <row r="14" spans="1:12" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9433,10 +9443,10 @@
       <c r="C14" s="257">
         <v>0</v>
       </c>
-      <c r="D14" s="467">
-        <v>0</v>
-      </c>
-      <c r="E14" s="468"/>
+      <c r="D14" s="464">
+        <v>0</v>
+      </c>
+      <c r="E14" s="465"/>
       <c r="F14" s="257">
         <v>0</v>
       </c>
@@ -9450,11 +9460,11 @@
         <f>SUM(B14:H14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="471">
+      <c r="J14" s="468">
         <f>I14/6</f>
         <v>0</v>
       </c>
-      <c r="K14" s="472"/>
+      <c r="K14" s="469"/>
       <c r="L14" s="148"/>
     </row>
     <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -9470,16 +9480,16 @@
       <c r="A17" s="279" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="429" t="s">
+      <c r="B17" s="430" t="s">
         <v>195</v>
       </c>
-      <c r="C17" s="430"/>
-      <c r="D17" s="430"/>
-      <c r="E17" s="430"/>
-      <c r="F17" s="430"/>
-      <c r="G17" s="430"/>
-      <c r="H17" s="430"/>
-      <c r="I17" s="431"/>
+      <c r="C17" s="431"/>
+      <c r="D17" s="431"/>
+      <c r="E17" s="431"/>
+      <c r="F17" s="431"/>
+      <c r="G17" s="431"/>
+      <c r="H17" s="431"/>
+      <c r="I17" s="432"/>
       <c r="J17" s="18" t="s">
         <v>170</v>
       </c>
@@ -9495,16 +9505,16 @@
       <c r="A18" s="232" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="461" t="s">
+      <c r="B18" s="458" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="462"/>
-      <c r="D18" s="462"/>
-      <c r="E18" s="462"/>
-      <c r="F18" s="462"/>
-      <c r="G18" s="462"/>
-      <c r="H18" s="462"/>
-      <c r="I18" s="463"/>
+      <c r="C18" s="459"/>
+      <c r="D18" s="459"/>
+      <c r="E18" s="459"/>
+      <c r="F18" s="459"/>
+      <c r="G18" s="459"/>
+      <c r="H18" s="459"/>
+      <c r="I18" s="460"/>
       <c r="J18" s="146" t="s">
         <v>119</v>
       </c>
@@ -9518,19 +9528,19 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="314" t="s">
+      <c r="A19" s="343" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="456" t="s">
+      <c r="B19" s="470" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="457"/>
-      <c r="D19" s="457"/>
-      <c r="E19" s="457"/>
-      <c r="F19" s="457"/>
-      <c r="G19" s="457"/>
-      <c r="H19" s="457"/>
-      <c r="I19" s="457"/>
+      <c r="C19" s="471"/>
+      <c r="D19" s="471"/>
+      <c r="E19" s="471"/>
+      <c r="F19" s="471"/>
+      <c r="G19" s="471"/>
+      <c r="H19" s="471"/>
+      <c r="I19" s="471"/>
       <c r="J19" s="146" t="s">
         <v>197</v>
       </c>
@@ -9543,17 +9553,17 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="315"/>
-      <c r="B20" s="458" t="s">
+      <c r="A20" s="344"/>
+      <c r="B20" s="472" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="459"/>
-      <c r="D20" s="459"/>
-      <c r="E20" s="459"/>
-      <c r="F20" s="459"/>
-      <c r="G20" s="459"/>
-      <c r="H20" s="459"/>
-      <c r="I20" s="459"/>
+      <c r="C20" s="473"/>
+      <c r="D20" s="473"/>
+      <c r="E20" s="473"/>
+      <c r="F20" s="473"/>
+      <c r="G20" s="473"/>
+      <c r="H20" s="473"/>
+      <c r="I20" s="473"/>
       <c r="J20" s="144" t="s">
         <v>123</v>
       </c>
@@ -9678,6 +9688,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B17:I17"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="A2:I2"/>
@@ -9687,13 +9704,6 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="J14:K14"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="B17:I17"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="B14:H14 K19 K20 L23" xr:uid="{5C12642A-ECB8-442A-97E3-CEC6FE13045F}">
@@ -10304,17 +10314,17 @@
   <sheetData>
     <row r="1" spans="1:12" s="111" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="464" t="s">
+      <c r="A2" s="461" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="464"/>
-      <c r="C2" s="464"/>
-      <c r="D2" s="464"/>
-      <c r="E2" s="464"/>
-      <c r="F2" s="464"/>
-      <c r="G2" s="464"/>
-      <c r="H2" s="464"/>
-      <c r="I2" s="464"/>
+      <c r="B2" s="461"/>
+      <c r="C2" s="461"/>
+      <c r="D2" s="461"/>
+      <c r="E2" s="461"/>
+      <c r="F2" s="461"/>
+      <c r="G2" s="461"/>
+      <c r="H2" s="461"/>
+      <c r="I2" s="461"/>
       <c r="J2" s="141"/>
       <c r="K2" s="141"/>
       <c r="L2" s="141"/>
@@ -10359,10 +10369,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="G5" s="140"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
@@ -10377,10 +10387,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="G6" s="139"/>
       <c r="H6" s="13"/>
       <c r="I6" s="14" t="s">
@@ -10411,10 +10421,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
       <c r="G8" s="149"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -10429,10 +10439,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
       <c r="G9" s="149"/>
       <c r="H9" s="139"/>
       <c r="I9" s="139"/>
@@ -10445,15 +10455,15 @@
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
       <c r="G10" s="149"/>
       <c r="H10" s="139"/>
       <c r="I10" s="139"/>
-      <c r="J10" s="460"/>
-      <c r="K10" s="460"/>
+      <c r="J10" s="457"/>
+      <c r="K10" s="457"/>
       <c r="L10" s="150"/>
     </row>
     <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -10480,10 +10490,10 @@
       <c r="C13" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="465" t="s">
+      <c r="D13" s="462" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="466"/>
+      <c r="E13" s="463"/>
       <c r="F13" s="237" t="s">
         <v>116</v>
       </c>
@@ -10492,10 +10502,10 @@
       <c r="I13" s="239" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="469" t="s">
+      <c r="J13" s="466" t="s">
         <v>121</v>
       </c>
-      <c r="K13" s="470"/>
+      <c r="K13" s="467"/>
       <c r="L13" s="148"/>
     </row>
     <row r="14" spans="1:12" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10505,10 +10515,10 @@
       <c r="C14" s="257">
         <v>0</v>
       </c>
-      <c r="D14" s="467">
-        <v>0</v>
-      </c>
-      <c r="E14" s="468"/>
+      <c r="D14" s="464">
+        <v>0</v>
+      </c>
+      <c r="E14" s="465"/>
       <c r="F14" s="257">
         <v>0</v>
       </c>
@@ -10518,11 +10528,11 @@
         <f>SUM(B14:F14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="471">
+      <c r="J14" s="468">
         <f>I14/4</f>
         <v>0</v>
       </c>
-      <c r="K14" s="472"/>
+      <c r="K14" s="469"/>
       <c r="L14" s="148"/>
     </row>
     <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10538,16 +10548,16 @@
       <c r="A17" s="279" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="429" t="s">
+      <c r="B17" s="430" t="s">
         <v>195</v>
       </c>
-      <c r="C17" s="430"/>
-      <c r="D17" s="430"/>
-      <c r="E17" s="430"/>
-      <c r="F17" s="430"/>
-      <c r="G17" s="430"/>
-      <c r="H17" s="430"/>
-      <c r="I17" s="431"/>
+      <c r="C17" s="431"/>
+      <c r="D17" s="431"/>
+      <c r="E17" s="431"/>
+      <c r="F17" s="431"/>
+      <c r="G17" s="431"/>
+      <c r="H17" s="431"/>
+      <c r="I17" s="432"/>
       <c r="J17" s="18" t="s">
         <v>170</v>
       </c>
@@ -10563,16 +10573,16 @@
       <c r="A18" s="232" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="473" t="s">
+      <c r="B18" s="474" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="474"/>
-      <c r="D18" s="474"/>
-      <c r="E18" s="474"/>
-      <c r="F18" s="474"/>
-      <c r="G18" s="474"/>
-      <c r="H18" s="474"/>
-      <c r="I18" s="475"/>
+      <c r="C18" s="475"/>
+      <c r="D18" s="475"/>
+      <c r="E18" s="475"/>
+      <c r="F18" s="475"/>
+      <c r="G18" s="475"/>
+      <c r="H18" s="475"/>
+      <c r="I18" s="476"/>
       <c r="J18" s="146" t="s">
         <v>119</v>
       </c>
@@ -10586,19 +10596,19 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="314" t="s">
+      <c r="A19" s="343" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="456" t="s">
+      <c r="B19" s="470" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="457"/>
-      <c r="D19" s="457"/>
-      <c r="E19" s="457"/>
-      <c r="F19" s="457"/>
-      <c r="G19" s="457"/>
-      <c r="H19" s="457"/>
-      <c r="I19" s="457"/>
+      <c r="C19" s="471"/>
+      <c r="D19" s="471"/>
+      <c r="E19" s="471"/>
+      <c r="F19" s="471"/>
+      <c r="G19" s="471"/>
+      <c r="H19" s="471"/>
+      <c r="I19" s="471"/>
       <c r="J19" s="146" t="s">
         <v>197</v>
       </c>
@@ -10611,17 +10621,17 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="315"/>
-      <c r="B20" s="458" t="s">
+      <c r="A20" s="344"/>
+      <c r="B20" s="472" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="459"/>
-      <c r="D20" s="459"/>
-      <c r="E20" s="459"/>
-      <c r="F20" s="459"/>
-      <c r="G20" s="459"/>
-      <c r="H20" s="459"/>
-      <c r="I20" s="459"/>
+      <c r="C20" s="473"/>
+      <c r="D20" s="473"/>
+      <c r="E20" s="473"/>
+      <c r="F20" s="473"/>
+      <c r="G20" s="473"/>
+      <c r="H20" s="473"/>
+      <c r="I20" s="473"/>
       <c r="J20" s="144" t="s">
         <v>123</v>
       </c>
@@ -10744,6 +10754,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B20:I20"/>
@@ -10755,11 +10770,6 @@
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="B17:I17"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="B14:F14 K19 K20 L23" xr:uid="{F4EB1C43-753F-4EC3-B376-2665BC2F486C}">
@@ -10831,8 +10841,8 @@
         <v>4</v>
       </c>
       <c r="B3" s="158"/>
-      <c r="C3" s="308"/>
-      <c r="D3" s="308"/>
+      <c r="C3" s="369"/>
+      <c r="D3" s="369"/>
       <c r="E3" s="265"/>
       <c r="F3" s="265"/>
       <c r="H3" s="153"/>
@@ -10848,10 +10858,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="134"/>
-      <c r="C4" s="307"/>
-      <c r="D4" s="307"/>
-      <c r="E4" s="307"/>
-      <c r="F4" s="307"/>
+      <c r="C4" s="368"/>
+      <c r="D4" s="368"/>
+      <c r="E4" s="368"/>
+      <c r="F4" s="368"/>
       <c r="H4" s="153"/>
       <c r="I4" s="154" t="s">
         <v>11</v>
@@ -10865,10 +10875,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="134"/>
-      <c r="C5" s="307"/>
-      <c r="D5" s="307"/>
-      <c r="E5" s="307"/>
-      <c r="F5" s="307"/>
+      <c r="C5" s="368"/>
+      <c r="D5" s="368"/>
+      <c r="E5" s="368"/>
+      <c r="F5" s="368"/>
       <c r="K5" s="30"/>
     </row>
     <row r="6" spans="1:12" s="111" customFormat="1" ht="17.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10891,10 +10901,10 @@
         <v>0</v>
       </c>
       <c r="B7" s="158"/>
-      <c r="C7" s="307"/>
-      <c r="D7" s="307"/>
-      <c r="E7" s="307"/>
-      <c r="F7" s="307"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
       <c r="K7" s="30"/>
     </row>
     <row r="8" spans="1:12" s="111" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -10902,10 +10912,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="134"/>
-      <c r="C8" s="307"/>
-      <c r="D8" s="307"/>
-      <c r="E8" s="307"/>
-      <c r="F8" s="307"/>
+      <c r="C8" s="368"/>
+      <c r="D8" s="368"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="K8" s="30"/>
     </row>
     <row r="9" spans="1:12" s="111" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -10913,10 +10923,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="134"/>
-      <c r="C9" s="307"/>
-      <c r="D9" s="307"/>
-      <c r="E9" s="307"/>
-      <c r="F9" s="307"/>
+      <c r="C9" s="368"/>
+      <c r="D9" s="368"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="K9" s="30"/>
     </row>
     <row r="10" spans="1:12" s="111" customFormat="1" ht="17.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10931,90 +10941,90 @@
       <c r="D11" s="268"/>
       <c r="E11" s="268"/>
       <c r="F11" s="268"/>
-      <c r="H11" s="309" t="s">
+      <c r="H11" s="338" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="310"/>
-      <c r="J11" s="311" t="s">
+      <c r="I11" s="339"/>
+      <c r="J11" s="340" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="312"/>
-      <c r="L11" s="313"/>
+      <c r="K11" s="341"/>
+      <c r="L11" s="342"/>
     </row>
     <row r="12" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="314" t="s">
+      <c r="A12" s="343" t="s">
         <v>138</v>
       </c>
-      <c r="B12" s="318" t="s">
+      <c r="B12" s="347" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="319"/>
-      <c r="D12" s="319"/>
-      <c r="E12" s="319"/>
-      <c r="F12" s="319"/>
-      <c r="G12" s="320"/>
-      <c r="H12" s="327"/>
-      <c r="I12" s="328"/>
-      <c r="J12" s="333" t="s">
+      <c r="C12" s="348"/>
+      <c r="D12" s="348"/>
+      <c r="E12" s="348"/>
+      <c r="F12" s="348"/>
+      <c r="G12" s="349"/>
+      <c r="H12" s="356"/>
+      <c r="I12" s="357"/>
+      <c r="J12" s="362" t="s">
         <v>140</v>
       </c>
-      <c r="K12" s="336">
+      <c r="K12" s="364">
         <f>SUM(B17:G17)/6</f>
         <v>0</v>
       </c>
-      <c r="L12" s="338">
+      <c r="L12" s="366">
         <f>ROUND(K12*0.6,3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="315"/>
-      <c r="B13" s="321"/>
-      <c r="C13" s="322"/>
-      <c r="D13" s="322"/>
-      <c r="E13" s="322"/>
-      <c r="F13" s="322"/>
-      <c r="G13" s="323"/>
-      <c r="H13" s="329"/>
-      <c r="I13" s="330"/>
-      <c r="J13" s="334"/>
-      <c r="K13" s="337"/>
-      <c r="L13" s="339"/>
+      <c r="A13" s="344"/>
+      <c r="B13" s="350"/>
+      <c r="C13" s="351"/>
+      <c r="D13" s="351"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
+      <c r="G13" s="352"/>
+      <c r="H13" s="358"/>
+      <c r="I13" s="359"/>
+      <c r="J13" s="324"/>
+      <c r="K13" s="365"/>
+      <c r="L13" s="326"/>
     </row>
     <row r="14" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="315"/>
-      <c r="B14" s="321"/>
-      <c r="C14" s="322"/>
-      <c r="D14" s="322"/>
-      <c r="E14" s="322"/>
-      <c r="F14" s="322"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="329"/>
-      <c r="I14" s="330"/>
-      <c r="J14" s="334"/>
-      <c r="K14" s="337"/>
-      <c r="L14" s="339"/>
+      <c r="A14" s="344"/>
+      <c r="B14" s="350"/>
+      <c r="C14" s="351"/>
+      <c r="D14" s="351"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
+      <c r="G14" s="352"/>
+      <c r="H14" s="358"/>
+      <c r="I14" s="359"/>
+      <c r="J14" s="324"/>
+      <c r="K14" s="365"/>
+      <c r="L14" s="326"/>
     </row>
     <row r="15" spans="1:12" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="315"/>
-      <c r="B15" s="324"/>
-      <c r="C15" s="325"/>
-      <c r="D15" s="325"/>
-      <c r="E15" s="325"/>
-      <c r="F15" s="325"/>
-      <c r="G15" s="326"/>
-      <c r="H15" s="329"/>
-      <c r="I15" s="330"/>
-      <c r="J15" s="334"/>
-      <c r="K15" s="337"/>
-      <c r="L15" s="339"/>
+      <c r="A15" s="344"/>
+      <c r="B15" s="353"/>
+      <c r="C15" s="354"/>
+      <c r="D15" s="354"/>
+      <c r="E15" s="354"/>
+      <c r="F15" s="354"/>
+      <c r="G15" s="355"/>
+      <c r="H15" s="358"/>
+      <c r="I15" s="359"/>
+      <c r="J15" s="324"/>
+      <c r="K15" s="365"/>
+      <c r="L15" s="326"/>
     </row>
     <row r="16" spans="1:12" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="316"/>
+      <c r="A16" s="345"/>
       <c r="B16" s="293" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="476" t="s">
+      <c r="C16" s="298" t="s">
         <v>142</v>
       </c>
       <c r="D16" s="295" t="s">
@@ -11029,154 +11039,154 @@
       <c r="G16" s="296" t="s">
         <v>146</v>
       </c>
-      <c r="H16" s="329"/>
-      <c r="I16" s="330"/>
-      <c r="J16" s="334"/>
-      <c r="K16" s="337"/>
-      <c r="L16" s="339"/>
+      <c r="H16" s="358"/>
+      <c r="I16" s="359"/>
+      <c r="J16" s="324"/>
+      <c r="K16" s="365"/>
+      <c r="L16" s="326"/>
     </row>
     <row r="17" spans="1:12" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="317"/>
+      <c r="A17" s="346"/>
       <c r="B17" s="269"/>
       <c r="C17" s="270"/>
       <c r="D17" s="270"/>
       <c r="E17" s="270"/>
       <c r="F17" s="270"/>
       <c r="G17" s="271"/>
-      <c r="H17" s="331"/>
-      <c r="I17" s="332"/>
-      <c r="J17" s="335"/>
-      <c r="K17" s="337"/>
-      <c r="L17" s="340"/>
+      <c r="H17" s="360"/>
+      <c r="I17" s="361"/>
+      <c r="J17" s="363"/>
+      <c r="K17" s="365"/>
+      <c r="L17" s="367"/>
     </row>
     <row r="18" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="343"/>
-      <c r="B18" s="346" t="s">
+      <c r="A18" s="301"/>
+      <c r="B18" s="304" t="s">
         <v>193</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
-      <c r="G18" s="346"/>
-      <c r="H18" s="348"/>
-      <c r="I18" s="349"/>
-      <c r="J18" s="354" t="s">
+      <c r="C18" s="304"/>
+      <c r="D18" s="304"/>
+      <c r="E18" s="304"/>
+      <c r="F18" s="304"/>
+      <c r="G18" s="304"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="307"/>
+      <c r="J18" s="312" t="s">
         <v>1</v>
       </c>
-      <c r="K18" s="375">
+      <c r="K18" s="335">
         <f>SUMPRODUCT(B23:G23,B22:G22)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="357" t="str">
+      <c r="L18" s="315" t="str">
         <f>IF(K18=0,"",MAX(0.0000000001,IF(K25="",ROUND(K18*0.25,3),ROUND((K18-K25)*0.25,3))))</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="344"/>
-      <c r="B19" s="347"/>
-      <c r="C19" s="347"/>
-      <c r="D19" s="347"/>
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
-      <c r="G19" s="347"/>
-      <c r="H19" s="350"/>
-      <c r="I19" s="351"/>
-      <c r="J19" s="355"/>
-      <c r="K19" s="376"/>
-      <c r="L19" s="358"/>
+      <c r="A19" s="302"/>
+      <c r="B19" s="305"/>
+      <c r="C19" s="305"/>
+      <c r="D19" s="305"/>
+      <c r="E19" s="305"/>
+      <c r="F19" s="305"/>
+      <c r="G19" s="305"/>
+      <c r="H19" s="308"/>
+      <c r="I19" s="309"/>
+      <c r="J19" s="313"/>
+      <c r="K19" s="336"/>
+      <c r="L19" s="316"/>
     </row>
     <row r="20" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="344"/>
-      <c r="B20" s="347"/>
-      <c r="C20" s="347"/>
-      <c r="D20" s="347"/>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
-      <c r="G20" s="347"/>
-      <c r="H20" s="350"/>
-      <c r="I20" s="351"/>
-      <c r="J20" s="355"/>
-      <c r="K20" s="376"/>
-      <c r="L20" s="358"/>
+      <c r="A20" s="302"/>
+      <c r="B20" s="305"/>
+      <c r="C20" s="305"/>
+      <c r="D20" s="305"/>
+      <c r="E20" s="305"/>
+      <c r="F20" s="305"/>
+      <c r="G20" s="305"/>
+      <c r="H20" s="308"/>
+      <c r="I20" s="309"/>
+      <c r="J20" s="313"/>
+      <c r="K20" s="336"/>
+      <c r="L20" s="316"/>
     </row>
     <row r="21" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="344"/>
-      <c r="B21" s="367" t="s">
+      <c r="A21" s="302"/>
+      <c r="B21" s="327" t="s">
         <v>190</v>
       </c>
-      <c r="C21" s="368"/>
-      <c r="D21" s="369" t="s">
+      <c r="C21" s="328"/>
+      <c r="D21" s="329" t="s">
         <v>191</v>
       </c>
-      <c r="E21" s="370"/>
-      <c r="F21" s="371" t="s">
+      <c r="E21" s="330"/>
+      <c r="F21" s="331" t="s">
         <v>192</v>
       </c>
-      <c r="G21" s="372"/>
-      <c r="H21" s="350"/>
-      <c r="I21" s="351"/>
-      <c r="J21" s="355"/>
-      <c r="K21" s="376"/>
-      <c r="L21" s="358"/>
+      <c r="G21" s="332"/>
+      <c r="H21" s="308"/>
+      <c r="I21" s="309"/>
+      <c r="J21" s="313"/>
+      <c r="K21" s="336"/>
+      <c r="L21" s="316"/>
     </row>
     <row r="22" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="344"/>
-      <c r="B22" s="373">
+      <c r="A22" s="302"/>
+      <c r="B22" s="333">
         <v>0.5</v>
       </c>
-      <c r="C22" s="374"/>
-      <c r="D22" s="298">
+      <c r="C22" s="334"/>
+      <c r="D22" s="370">
         <v>0.25</v>
       </c>
-      <c r="E22" s="299"/>
-      <c r="F22" s="300">
+      <c r="E22" s="371"/>
+      <c r="F22" s="372">
         <v>0.25</v>
       </c>
-      <c r="G22" s="301"/>
-      <c r="H22" s="350"/>
-      <c r="I22" s="351"/>
-      <c r="J22" s="355"/>
-      <c r="K22" s="376"/>
-      <c r="L22" s="358"/>
+      <c r="G22" s="373"/>
+      <c r="H22" s="308"/>
+      <c r="I22" s="309"/>
+      <c r="J22" s="313"/>
+      <c r="K22" s="336"/>
+      <c r="L22" s="316"/>
     </row>
     <row r="23" spans="1:12" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="344"/>
-      <c r="B23" s="302">
-        <v>0</v>
-      </c>
-      <c r="C23" s="303"/>
-      <c r="D23" s="304">
-        <v>0</v>
-      </c>
-      <c r="E23" s="305"/>
-      <c r="F23" s="303">
-        <v>0</v>
-      </c>
-      <c r="G23" s="306"/>
-      <c r="H23" s="350"/>
-      <c r="I23" s="351"/>
-      <c r="J23" s="355"/>
-      <c r="K23" s="376"/>
-      <c r="L23" s="358"/>
+      <c r="A23" s="302"/>
+      <c r="B23" s="374">
+        <v>0</v>
+      </c>
+      <c r="C23" s="375"/>
+      <c r="D23" s="376">
+        <v>0</v>
+      </c>
+      <c r="E23" s="377"/>
+      <c r="F23" s="375">
+        <v>0</v>
+      </c>
+      <c r="G23" s="378"/>
+      <c r="H23" s="308"/>
+      <c r="I23" s="309"/>
+      <c r="J23" s="313"/>
+      <c r="K23" s="336"/>
+      <c r="L23" s="316"/>
     </row>
     <row r="24" spans="1:12" s="148" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="344"/>
+      <c r="A24" s="302"/>
       <c r="B24" s="284"/>
       <c r="C24" s="285"/>
       <c r="D24" s="286"/>
       <c r="E24" s="286"/>
       <c r="F24" s="285"/>
       <c r="G24" s="287"/>
-      <c r="H24" s="350"/>
-      <c r="I24" s="351"/>
-      <c r="J24" s="355"/>
-      <c r="K24" s="377"/>
-      <c r="L24" s="358"/>
+      <c r="H24" s="308"/>
+      <c r="I24" s="309"/>
+      <c r="J24" s="313"/>
+      <c r="K24" s="337"/>
+      <c r="L24" s="316"/>
     </row>
     <row r="25" spans="1:12" ht="28.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="345"/>
+      <c r="A25" s="303"/>
       <c r="B25" s="272" t="s">
         <v>147</v>
       </c>
@@ -11187,42 +11197,42 @@
       <c r="E25" s="273"/>
       <c r="F25" s="273"/>
       <c r="G25" s="273"/>
-      <c r="H25" s="352"/>
-      <c r="I25" s="353"/>
-      <c r="J25" s="356"/>
+      <c r="H25" s="310"/>
+      <c r="I25" s="311"/>
+      <c r="J25" s="314"/>
       <c r="K25" s="288" t="str">
         <f>IF(SUM(C25:G25)=0,"",MAX(0.0000000001,SUM(C25:G25)))</f>
         <v/>
       </c>
-      <c r="L25" s="359"/>
+      <c r="L25" s="317"/>
     </row>
     <row r="26" spans="1:12" ht="107.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="343" t="s">
+      <c r="A26" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="346" t="s">
+      <c r="B26" s="304" t="s">
         <v>194</v>
       </c>
-      <c r="C26" s="360"/>
-      <c r="D26" s="360"/>
-      <c r="E26" s="360"/>
-      <c r="F26" s="360"/>
-      <c r="G26" s="361"/>
-      <c r="H26" s="362"/>
-      <c r="I26" s="363"/>
-      <c r="J26" s="334" t="s">
+      <c r="C26" s="318"/>
+      <c r="D26" s="318"/>
+      <c r="E26" s="318"/>
+      <c r="F26" s="318"/>
+      <c r="G26" s="319"/>
+      <c r="H26" s="320"/>
+      <c r="I26" s="321"/>
+      <c r="J26" s="324" t="s">
         <v>148</v>
       </c>
       <c r="K26" s="289">
         <v>0</v>
       </c>
-      <c r="L26" s="339">
+      <c r="L26" s="326">
         <f>IF((K26-K27)&gt;=0,(ROUND((K26-K27)*0.15,3)),0.000000001)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="345"/>
+      <c r="A27" s="303"/>
       <c r="B27" s="274" t="s">
         <v>147</v>
       </c>
@@ -11241,14 +11251,14 @@
       <c r="G27" s="273">
         <v>0</v>
       </c>
-      <c r="H27" s="364"/>
-      <c r="I27" s="365"/>
-      <c r="J27" s="366"/>
+      <c r="H27" s="322"/>
+      <c r="I27" s="323"/>
+      <c r="J27" s="325"/>
       <c r="K27" s="290">
         <f>SUM(C27:G27)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="359"/>
+      <c r="L27" s="317"/>
     </row>
     <row r="28" spans="1:12" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="21"/>
@@ -11265,11 +11275,11 @@
         <v>3</v>
       </c>
       <c r="J29" s="23"/>
-      <c r="K29" s="341">
+      <c r="K29" s="299">
         <f>SUM(L12:L26)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="342"/>
+      <c r="L29" s="300"/>
     </row>
     <row r="30" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11292,6 +11302,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:G15"/>
+    <mergeCell ref="H12:I17"/>
+    <mergeCell ref="J12:J17"/>
+    <mergeCell ref="K12:K17"/>
+    <mergeCell ref="L12:L17"/>
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="A18:A25"/>
     <mergeCell ref="B18:G20"/>
@@ -11308,25 +11337,6 @@
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="K18:K24"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:G15"/>
-    <mergeCell ref="H12:I17"/>
-    <mergeCell ref="J12:J17"/>
-    <mergeCell ref="K12:K17"/>
-    <mergeCell ref="L12:L17"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Enbart siffror" error="Ej giltig siffra_x000a_Kan du ha skirvit komma istället för punkt eller tvärt om" sqref="B17:G17 B23:C23 D23:E23 F23:G23 C25 D25 E25 F25 G25 C27 D27 E27 F27 G27 K26" xr:uid="{2F8E46EA-E6B1-42D6-9781-DACEBCFB30BC}">
@@ -11413,10 +11423,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="134"/>
-      <c r="C5" s="392"/>
-      <c r="D5" s="392"/>
-      <c r="E5" s="392"/>
-      <c r="F5" s="392"/>
+      <c r="C5" s="379"/>
+      <c r="D5" s="379"/>
+      <c r="E5" s="379"/>
+      <c r="F5" s="379"/>
       <c r="H5" s="153"/>
       <c r="I5" s="154" t="s">
         <v>11</v>
@@ -11430,10 +11440,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="134"/>
-      <c r="C6" s="392"/>
-      <c r="D6" s="392"/>
-      <c r="E6" s="392"/>
-      <c r="F6" s="392"/>
+      <c r="C6" s="379"/>
+      <c r="D6" s="379"/>
+      <c r="E6" s="379"/>
+      <c r="F6" s="379"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11456,30 +11466,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="158"/>
-      <c r="C8" s="392"/>
-      <c r="D8" s="392"/>
-      <c r="E8" s="392"/>
-      <c r="F8" s="392"/>
+      <c r="C8" s="379"/>
+      <c r="D8" s="379"/>
+      <c r="E8" s="379"/>
+      <c r="F8" s="379"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="134" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="134"/>
-      <c r="C9" s="392"/>
-      <c r="D9" s="392"/>
-      <c r="E9" s="392"/>
-      <c r="F9" s="392"/>
+      <c r="C9" s="379"/>
+      <c r="D9" s="379"/>
+      <c r="E9" s="379"/>
+      <c r="F9" s="379"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="134" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="134"/>
-      <c r="C10" s="392"/>
-      <c r="D10" s="392"/>
-      <c r="E10" s="392"/>
-      <c r="F10" s="392"/>
+      <c r="C10" s="379"/>
+      <c r="D10" s="379"/>
+      <c r="E10" s="379"/>
+      <c r="F10" s="379"/>
     </row>
     <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="57.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11503,115 +11513,115 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="378" t="s">
+      <c r="A15" s="380" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="379"/>
-      <c r="C15" s="379"/>
-      <c r="D15" s="380"/>
-      <c r="E15" s="384"/>
-      <c r="F15" s="385"/>
-      <c r="G15" s="385"/>
-      <c r="H15" s="385"/>
-      <c r="I15" s="385"/>
-      <c r="J15" s="385"/>
-      <c r="K15" s="386"/>
+      <c r="B15" s="381"/>
+      <c r="C15" s="381"/>
+      <c r="D15" s="382"/>
+      <c r="E15" s="386"/>
+      <c r="F15" s="387"/>
+      <c r="G15" s="387"/>
+      <c r="H15" s="387"/>
+      <c r="I15" s="387"/>
+      <c r="J15" s="387"/>
+      <c r="K15" s="388"/>
       <c r="L15" s="244"/>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="378" t="s">
+      <c r="A16" s="380" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="379"/>
-      <c r="C16" s="379"/>
-      <c r="D16" s="380"/>
-      <c r="E16" s="384"/>
-      <c r="F16" s="385"/>
-      <c r="G16" s="385"/>
-      <c r="H16" s="385"/>
-      <c r="I16" s="385"/>
-      <c r="J16" s="385"/>
-      <c r="K16" s="386"/>
+      <c r="B16" s="381"/>
+      <c r="C16" s="381"/>
+      <c r="D16" s="382"/>
+      <c r="E16" s="386"/>
+      <c r="F16" s="387"/>
+      <c r="G16" s="387"/>
+      <c r="H16" s="387"/>
+      <c r="I16" s="387"/>
+      <c r="J16" s="387"/>
+      <c r="K16" s="388"/>
       <c r="L16" s="244"/>
     </row>
     <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="381" t="s">
+      <c r="A17" s="383" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="382"/>
-      <c r="C17" s="382"/>
-      <c r="D17" s="383"/>
-      <c r="E17" s="384"/>
-      <c r="F17" s="385"/>
-      <c r="G17" s="385"/>
-      <c r="H17" s="385"/>
-      <c r="I17" s="385"/>
-      <c r="J17" s="385"/>
-      <c r="K17" s="386"/>
+      <c r="B17" s="384"/>
+      <c r="C17" s="384"/>
+      <c r="D17" s="385"/>
+      <c r="E17" s="386"/>
+      <c r="F17" s="387"/>
+      <c r="G17" s="387"/>
+      <c r="H17" s="387"/>
+      <c r="I17" s="387"/>
+      <c r="J17" s="387"/>
+      <c r="K17" s="388"/>
       <c r="L17" s="244"/>
     </row>
     <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="378" t="s">
+      <c r="A18" s="380" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="379"/>
-      <c r="C18" s="379"/>
-      <c r="D18" s="380"/>
-      <c r="E18" s="384"/>
-      <c r="F18" s="385"/>
-      <c r="G18" s="385"/>
-      <c r="H18" s="385"/>
-      <c r="I18" s="385"/>
-      <c r="J18" s="385"/>
-      <c r="K18" s="386"/>
+      <c r="B18" s="381"/>
+      <c r="C18" s="381"/>
+      <c r="D18" s="382"/>
+      <c r="E18" s="386"/>
+      <c r="F18" s="387"/>
+      <c r="G18" s="387"/>
+      <c r="H18" s="387"/>
+      <c r="I18" s="387"/>
+      <c r="J18" s="387"/>
+      <c r="K18" s="388"/>
       <c r="L18" s="244"/>
     </row>
     <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="378" t="s">
+      <c r="A19" s="380" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="379"/>
-      <c r="C19" s="379"/>
-      <c r="D19" s="380"/>
-      <c r="E19" s="387"/>
-      <c r="F19" s="387"/>
-      <c r="G19" s="387"/>
-      <c r="H19" s="387"/>
-      <c r="I19" s="387"/>
-      <c r="J19" s="387"/>
-      <c r="K19" s="388"/>
+      <c r="B19" s="381"/>
+      <c r="C19" s="381"/>
+      <c r="D19" s="382"/>
+      <c r="E19" s="389"/>
+      <c r="F19" s="389"/>
+      <c r="G19" s="389"/>
+      <c r="H19" s="389"/>
+      <c r="I19" s="389"/>
+      <c r="J19" s="389"/>
+      <c r="K19" s="390"/>
       <c r="L19" s="244"/>
     </row>
     <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="389" t="s">
+      <c r="A20" s="391" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="390"/>
-      <c r="C20" s="390"/>
-      <c r="D20" s="391"/>
-      <c r="E20" s="384"/>
-      <c r="F20" s="385"/>
-      <c r="G20" s="385"/>
-      <c r="H20" s="385"/>
-      <c r="I20" s="385"/>
-      <c r="J20" s="385"/>
-      <c r="K20" s="386"/>
+      <c r="B20" s="392"/>
+      <c r="C20" s="392"/>
+      <c r="D20" s="393"/>
+      <c r="E20" s="386"/>
+      <c r="F20" s="387"/>
+      <c r="G20" s="387"/>
+      <c r="H20" s="387"/>
+      <c r="I20" s="387"/>
+      <c r="J20" s="387"/>
+      <c r="K20" s="388"/>
       <c r="L20" s="244"/>
     </row>
     <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="378" t="s">
+      <c r="A21" s="380" t="s">
         <v>178</v>
       </c>
-      <c r="B21" s="379"/>
-      <c r="C21" s="379"/>
-      <c r="D21" s="380"/>
-      <c r="E21" s="378"/>
-      <c r="F21" s="379"/>
-      <c r="G21" s="379"/>
-      <c r="H21" s="379"/>
-      <c r="I21" s="379"/>
-      <c r="J21" s="379"/>
-      <c r="K21" s="380"/>
+      <c r="B21" s="381"/>
+      <c r="C21" s="381"/>
+      <c r="D21" s="382"/>
+      <c r="E21" s="380"/>
+      <c r="F21" s="381"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
+      <c r="I21" s="381"/>
+      <c r="J21" s="381"/>
+      <c r="K21" s="382"/>
       <c r="L21" s="244"/>
     </row>
     <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11720,11 +11730,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
     <mergeCell ref="E21:K21"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A17:D17"/>
@@ -11739,6 +11744,11 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Du kan endast mata in siffror mellan 0 och 10. Var noga med punkt eller komma beroende på språk" sqref="L15:L21" xr:uid="{8720CD5A-D7F9-401B-93A9-DA40D5B20AB8}">
@@ -11827,10 +11837,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -11844,10 +11854,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11870,30 +11880,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12029,13 +12039,13 @@
       <c r="L21" s="245"/>
     </row>
     <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="393" t="s">
+      <c r="A22" s="394" t="s">
         <v>167</v>
       </c>
-      <c r="B22" s="394"/>
-      <c r="C22" s="394"/>
-      <c r="D22" s="394"/>
-      <c r="E22" s="395"/>
+      <c r="B22" s="395"/>
+      <c r="C22" s="395"/>
+      <c r="D22" s="395"/>
+      <c r="E22" s="396"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33"/>
       <c r="H22" s="33"/>
@@ -12232,10 +12242,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -12249,10 +12259,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12275,30 +12285,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12434,12 +12444,12 @@
       <c r="L21" s="245"/>
     </row>
     <row r="22" spans="1:12" ht="32.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="393" t="s">
+      <c r="A22" s="394" t="s">
         <v>199</v>
       </c>
-      <c r="B22" s="394"/>
-      <c r="C22" s="394"/>
-      <c r="D22" s="395"/>
+      <c r="B22" s="395"/>
+      <c r="C22" s="395"/>
+      <c r="D22" s="396"/>
       <c r="E22" s="33"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33"/>
@@ -12595,14 +12605,14 @@
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="404" t="s">
+      <c r="A2" s="405" t="s">
         <v>165</v>
       </c>
-      <c r="B2" s="404"/>
-      <c r="C2" s="404"/>
-      <c r="D2" s="404"/>
-      <c r="E2" s="404"/>
-      <c r="F2" s="404"/>
+      <c r="B2" s="405"/>
+      <c r="C2" s="405"/>
+      <c r="D2" s="405"/>
+      <c r="E2" s="405"/>
+      <c r="F2" s="405"/>
       <c r="H2" s="153"/>
       <c r="I2" s="154" t="s">
         <v>59</v>
@@ -12645,10 +12655,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="134"/>
-      <c r="C5" s="392"/>
-      <c r="D5" s="392"/>
-      <c r="E5" s="392"/>
-      <c r="F5" s="392"/>
+      <c r="C5" s="379"/>
+      <c r="D5" s="379"/>
+      <c r="E5" s="379"/>
+      <c r="F5" s="379"/>
       <c r="H5" s="153"/>
       <c r="I5" s="154" t="s">
         <v>11</v>
@@ -12662,10 +12672,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="134"/>
-      <c r="C6" s="392"/>
-      <c r="D6" s="392"/>
-      <c r="E6" s="392"/>
-      <c r="F6" s="392"/>
+      <c r="C6" s="379"/>
+      <c r="D6" s="379"/>
+      <c r="E6" s="379"/>
+      <c r="F6" s="379"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12688,30 +12698,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="158"/>
-      <c r="C8" s="405"/>
-      <c r="D8" s="405"/>
-      <c r="E8" s="405"/>
-      <c r="F8" s="405"/>
+      <c r="C8" s="406"/>
+      <c r="D8" s="406"/>
+      <c r="E8" s="406"/>
+      <c r="F8" s="406"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="134" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="134"/>
-      <c r="C9" s="392"/>
-      <c r="D9" s="392"/>
-      <c r="E9" s="392"/>
-      <c r="F9" s="392"/>
+      <c r="C9" s="379"/>
+      <c r="D9" s="379"/>
+      <c r="E9" s="379"/>
+      <c r="F9" s="379"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="134" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="134"/>
-      <c r="C10" s="392"/>
-      <c r="D10" s="392"/>
-      <c r="E10" s="392"/>
-      <c r="F10" s="392"/>
+      <c r="C10" s="379"/>
+      <c r="D10" s="379"/>
+      <c r="E10" s="379"/>
+      <c r="F10" s="379"/>
     </row>
     <row r="11" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -12738,32 +12748,32 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="398"/>
-      <c r="B13" s="399"/>
-      <c r="C13" s="399"/>
-      <c r="D13" s="399"/>
-      <c r="E13" s="399"/>
-      <c r="F13" s="399"/>
-      <c r="G13" s="399"/>
-      <c r="H13" s="399"/>
-      <c r="I13" s="399"/>
-      <c r="J13" s="399"/>
-      <c r="K13" s="399"/>
-      <c r="L13" s="400"/>
+      <c r="A13" s="399"/>
+      <c r="B13" s="400"/>
+      <c r="C13" s="400"/>
+      <c r="D13" s="400"/>
+      <c r="E13" s="400"/>
+      <c r="F13" s="400"/>
+      <c r="G13" s="400"/>
+      <c r="H13" s="400"/>
+      <c r="I13" s="400"/>
+      <c r="J13" s="400"/>
+      <c r="K13" s="400"/>
+      <c r="L13" s="401"/>
     </row>
     <row r="14" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="401"/>
-      <c r="B14" s="402"/>
-      <c r="C14" s="402"/>
-      <c r="D14" s="402"/>
-      <c r="E14" s="402"/>
-      <c r="F14" s="402"/>
-      <c r="G14" s="402"/>
-      <c r="H14" s="402"/>
-      <c r="I14" s="402"/>
-      <c r="J14" s="402"/>
-      <c r="K14" s="402"/>
-      <c r="L14" s="403"/>
+      <c r="A14" s="402"/>
+      <c r="B14" s="403"/>
+      <c r="C14" s="403"/>
+      <c r="D14" s="403"/>
+      <c r="E14" s="403"/>
+      <c r="F14" s="403"/>
+      <c r="G14" s="403"/>
+      <c r="H14" s="403"/>
+      <c r="I14" s="403"/>
+      <c r="J14" s="403"/>
+      <c r="K14" s="403"/>
+      <c r="L14" s="404"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="166" t="s">
@@ -13621,14 +13631,14 @@
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="406" t="s">
+      <c r="A2" s="407" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="406"/>
-      <c r="C2" s="406"/>
-      <c r="D2" s="406"/>
-      <c r="E2" s="406"/>
-      <c r="F2" s="406"/>
+      <c r="B2" s="407"/>
+      <c r="C2" s="407"/>
+      <c r="D2" s="407"/>
+      <c r="E2" s="407"/>
+      <c r="F2" s="407"/>
       <c r="H2" s="13"/>
       <c r="I2" s="14" t="s">
         <v>59</v>
@@ -13671,10 +13681,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -13688,10 +13698,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -13720,30 +13730,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -13770,32 +13780,32 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="407"/>
-      <c r="B13" s="408"/>
-      <c r="C13" s="408"/>
-      <c r="D13" s="408"/>
-      <c r="E13" s="408"/>
-      <c r="F13" s="408"/>
-      <c r="G13" s="408"/>
-      <c r="H13" s="408"/>
-      <c r="I13" s="408"/>
-      <c r="J13" s="408"/>
-      <c r="K13" s="408"/>
-      <c r="L13" s="409"/>
+      <c r="A13" s="408"/>
+      <c r="B13" s="409"/>
+      <c r="C13" s="409"/>
+      <c r="D13" s="409"/>
+      <c r="E13" s="409"/>
+      <c r="F13" s="409"/>
+      <c r="G13" s="409"/>
+      <c r="H13" s="409"/>
+      <c r="I13" s="409"/>
+      <c r="J13" s="409"/>
+      <c r="K13" s="409"/>
+      <c r="L13" s="410"/>
     </row>
     <row r="14" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="410"/>
-      <c r="B14" s="411"/>
-      <c r="C14" s="411"/>
-      <c r="D14" s="411"/>
-      <c r="E14" s="411"/>
-      <c r="F14" s="411"/>
-      <c r="G14" s="411"/>
-      <c r="H14" s="411"/>
-      <c r="I14" s="411"/>
-      <c r="J14" s="411"/>
-      <c r="K14" s="411"/>
-      <c r="L14" s="412"/>
+      <c r="A14" s="411"/>
+      <c r="B14" s="412"/>
+      <c r="C14" s="412"/>
+      <c r="D14" s="412"/>
+      <c r="E14" s="412"/>
+      <c r="F14" s="412"/>
+      <c r="G14" s="412"/>
+      <c r="H14" s="412"/>
+      <c r="I14" s="412"/>
+      <c r="J14" s="412"/>
+      <c r="K14" s="412"/>
+      <c r="L14" s="413"/>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
@@ -14808,10 +14818,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -14825,10 +14835,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -14857,30 +14867,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -14907,32 +14917,32 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="407"/>
-      <c r="B13" s="408"/>
-      <c r="C13" s="408"/>
-      <c r="D13" s="408"/>
-      <c r="E13" s="408"/>
-      <c r="F13" s="408"/>
-      <c r="G13" s="408"/>
-      <c r="H13" s="408"/>
-      <c r="I13" s="408"/>
-      <c r="J13" s="408"/>
-      <c r="K13" s="408"/>
-      <c r="L13" s="409"/>
+      <c r="A13" s="408"/>
+      <c r="B13" s="409"/>
+      <c r="C13" s="409"/>
+      <c r="D13" s="409"/>
+      <c r="E13" s="409"/>
+      <c r="F13" s="409"/>
+      <c r="G13" s="409"/>
+      <c r="H13" s="409"/>
+      <c r="I13" s="409"/>
+      <c r="J13" s="409"/>
+      <c r="K13" s="409"/>
+      <c r="L13" s="410"/>
     </row>
     <row r="14" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="410"/>
-      <c r="B14" s="411"/>
-      <c r="C14" s="411"/>
-      <c r="D14" s="411"/>
-      <c r="E14" s="411"/>
-      <c r="F14" s="411"/>
-      <c r="G14" s="411"/>
-      <c r="H14" s="411"/>
-      <c r="I14" s="411"/>
-      <c r="J14" s="411"/>
-      <c r="K14" s="411"/>
-      <c r="L14" s="412"/>
+      <c r="A14" s="411"/>
+      <c r="B14" s="412"/>
+      <c r="C14" s="412"/>
+      <c r="D14" s="412"/>
+      <c r="E14" s="412"/>
+      <c r="F14" s="412"/>
+      <c r="G14" s="412"/>
+      <c r="H14" s="412"/>
+      <c r="I14" s="412"/>
+      <c r="J14" s="412"/>
+      <c r="K14" s="412"/>
+      <c r="L14" s="413"/>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
@@ -15838,14 +15848,14 @@
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="406" t="s">
+      <c r="A2" s="407" t="s">
         <v>165</v>
       </c>
-      <c r="B2" s="406"/>
-      <c r="C2" s="406"/>
-      <c r="D2" s="406"/>
-      <c r="E2" s="406"/>
-      <c r="F2" s="406"/>
+      <c r="B2" s="407"/>
+      <c r="C2" s="407"/>
+      <c r="D2" s="407"/>
+      <c r="E2" s="407"/>
+      <c r="F2" s="407"/>
       <c r="H2" s="13"/>
       <c r="I2" s="14" t="s">
         <v>59</v>
@@ -15888,10 +15898,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="396"/>
-      <c r="D5" s="396"/>
-      <c r="E5" s="396"/>
-      <c r="F5" s="396"/>
+      <c r="C5" s="397"/>
+      <c r="D5" s="397"/>
+      <c r="E5" s="397"/>
+      <c r="F5" s="397"/>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
         <v>11</v>
@@ -15905,10 +15915,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="11"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396"/>
-      <c r="F6" s="396"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -15937,30 +15947,30 @@
         <v>0</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="397"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="397"/>
-      <c r="F8" s="397"/>
+      <c r="C8" s="398"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
     </row>
     <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="396"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
+      <c r="C9" s="397"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="396"/>
-      <c r="D10" s="396"/>
-      <c r="E10" s="396"/>
-      <c r="F10" s="396"/>
+      <c r="C10" s="397"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
     </row>
     <row r="11" spans="1:12" ht="10.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:12" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -15974,16 +15984,16 @@
       <c r="A13" s="279" t="s">
         <v>168</v>
       </c>
-      <c r="B13" s="429" t="s">
+      <c r="B13" s="430" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="430"/>
-      <c r="D13" s="430"/>
-      <c r="E13" s="430"/>
-      <c r="F13" s="430"/>
-      <c r="G13" s="430"/>
-      <c r="H13" s="430"/>
-      <c r="I13" s="431"/>
+      <c r="C13" s="431"/>
+      <c r="D13" s="431"/>
+      <c r="E13" s="431"/>
+      <c r="F13" s="431"/>
+      <c r="G13" s="431"/>
+      <c r="H13" s="431"/>
+      <c r="I13" s="432"/>
       <c r="J13" s="18" t="s">
         <v>170</v>
       </c>
@@ -15994,19 +16004,19 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="413" t="s">
+      <c r="A14" s="414" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="415" t="s">
+      <c r="B14" s="416" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="416"/>
-      <c r="D14" s="416"/>
-      <c r="E14" s="416"/>
-      <c r="F14" s="416"/>
-      <c r="G14" s="416"/>
-      <c r="H14" s="416"/>
-      <c r="I14" s="417"/>
+      <c r="C14" s="417"/>
+      <c r="D14" s="417"/>
+      <c r="E14" s="417"/>
+      <c r="F14" s="417"/>
+      <c r="G14" s="417"/>
+      <c r="H14" s="417"/>
+      <c r="I14" s="418"/>
       <c r="J14" s="18" t="s">
         <v>182</v>
       </c>
@@ -16017,17 +16027,17 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="414"/>
-      <c r="B15" s="418" t="s">
+      <c r="A15" s="415"/>
+      <c r="B15" s="419" t="s">
         <v>179</v>
       </c>
-      <c r="C15" s="419"/>
-      <c r="D15" s="419"/>
-      <c r="E15" s="419"/>
-      <c r="F15" s="419"/>
-      <c r="G15" s="419"/>
-      <c r="H15" s="419"/>
-      <c r="I15" s="420"/>
+      <c r="C15" s="420"/>
+      <c r="D15" s="420"/>
+      <c r="E15" s="420"/>
+      <c r="F15" s="420"/>
+      <c r="G15" s="420"/>
+      <c r="H15" s="420"/>
+      <c r="I15" s="421"/>
       <c r="J15" s="20" t="s">
         <v>183</v>
       </c>
@@ -16038,19 +16048,19 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="421" t="s">
+      <c r="A16" s="422" t="s">
         <v>201</v>
       </c>
-      <c r="B16" s="423" t="s">
+      <c r="B16" s="424" t="s">
         <v>180</v>
       </c>
-      <c r="C16" s="424"/>
-      <c r="D16" s="424"/>
-      <c r="E16" s="424"/>
-      <c r="F16" s="424"/>
-      <c r="G16" s="424"/>
-      <c r="H16" s="424"/>
-      <c r="I16" s="425"/>
+      <c r="C16" s="425"/>
+      <c r="D16" s="425"/>
+      <c r="E16" s="425"/>
+      <c r="F16" s="425"/>
+      <c r="G16" s="425"/>
+      <c r="H16" s="425"/>
+      <c r="I16" s="426"/>
       <c r="J16" s="18" t="s">
         <v>184</v>
       </c>
@@ -16061,17 +16071,17 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="422"/>
-      <c r="B17" s="426" t="s">
+      <c r="A17" s="423"/>
+      <c r="B17" s="427" t="s">
         <v>181</v>
       </c>
-      <c r="C17" s="427"/>
-      <c r="D17" s="427"/>
-      <c r="E17" s="427"/>
-      <c r="F17" s="427"/>
-      <c r="G17" s="427"/>
-      <c r="H17" s="427"/>
-      <c r="I17" s="428"/>
+      <c r="C17" s="428"/>
+      <c r="D17" s="428"/>
+      <c r="E17" s="428"/>
+      <c r="F17" s="428"/>
+      <c r="G17" s="428"/>
+      <c r="H17" s="428"/>
+      <c r="I17" s="429"/>
       <c r="J17" s="19" t="s">
         <v>185</v>
       </c>
@@ -16280,21 +16290,21 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16315,6 +16325,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A807C1-6DB8-4C6A-8DCB-8B5F61EFE299}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF64F18F-372D-43EC-AE22-C51BFB121B01}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -16327,12 +16345,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A807C1-6DB8-4C6A-8DCB-8B5F61EFE299}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>